--- a/health_tracking_forms/030_pet_sodium_intake_tracker_form--health_tracking_forms.xlsx
+++ b/health_tracking_forms/030_pet_sodium_intake_tracker_form--health_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'food'}</t>
+          <t>food</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'water'}</t>
+          <t>water</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'treats'}</t>
+          <t>treats</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'treats'}</t>
+          <t>treats</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'vet_clinic_1'}</t>
+          <t>vet_clinic_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'vet_clinic_1'}</t>
+          <t>vet clinic 1</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'vet_clinic_2'}</t>
+          <t>vet_clinic_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'vet_clinic_2'}</t>
+          <t>vet clinic 2</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'vet_clinic_3'}</t>
+          <t>vet_clinic_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'vet_clinic_3'}</t>
+          <t>vet clinic 3</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'female'}</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'male'}</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'overweight'}</t>
+          <t>overweight</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'overweight'}</t>
+          <t>overweight</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'obesity'}</t>
+          <t>obesity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'obesity'}</t>
+          <t>obesity</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'heart_condition'}</t>
+          <t>heart_condition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'heart_condition'}</t>
+          <t>heart condition</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'kidney_condition'}</t>
+          <t>kidney_condition</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'kidney_condition'}</t>
+          <t>kidney condition</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'joint_issue'}</t>
+          <t>joint_issue</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'joint_issue'}</t>
+          <t>joint issue</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'kidney_issue'}</t>
+          <t>kidney_issue</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'kidney_issue'}</t>
+          <t>kidney issue</t>
         </is>
       </c>
     </row>
